--- a/Team-Data/2012-13/3-21-2012-13.xlsx
+++ b/Team-Data/2012-13/3-21-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -921,22 +988,22 @@
         <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -996,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,10 +1182,10 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1157,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
         <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.537</v>
+        <v>0.545</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L6" t="n">
         <v>4.9</v>
@@ -1419,16 +1486,16 @@
         <v>14.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O6" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P6" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
@@ -1440,10 +1507,10 @@
         <v>43.4</v>
       </c>
       <c r="U6" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1455,28 +1522,28 @@
         <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.7</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1485,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>25</v>
@@ -1518,13 +1585,13 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1691,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1867,7 +1934,7 @@
         <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1953,19 +2020,19 @@
         <v>40.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0.478</v>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O9" t="n">
         <v>18</v>
@@ -1974,25 +2041,25 @@
         <v>25.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
       <c r="R9" t="n">
         <v>13.4</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="U9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>6.6</v>
@@ -2007,13 +2074,13 @@
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>106.1</v>
       </c>
       <c r="AC9" t="n">
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2043,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2234,7 +2301,7 @@
         <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2252,7 +2319,7 @@
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -2434,10 +2501,10 @@
         <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2813,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>13</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3299,7 +3366,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
         <v>21</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3323,7 +3390,7 @@
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -3755,49 +3822,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="n">
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
       </c>
       <c r="L19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.294</v>
+        <v>0.298</v>
       </c>
       <c r="O19" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S19" t="n">
         <v>30.2</v>
@@ -3806,7 +3873,7 @@
         <v>42.6</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
@@ -3821,37 +3888,37 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
         <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
         <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3875,7 +3942,7 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
         <v>18</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>24</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4215,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4579,7 +4646,7 @@
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
@@ -4612,7 +4679,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" t="n">
         <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J24" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L24" t="n">
         <v>6.2</v>
@@ -4695,55 +4762,55 @@
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
         <v>11.9</v>
       </c>
       <c r="P24" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="R24" t="n">
         <v>10.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>22.9</v>
       </c>
       <c r="V24" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
         <v>4.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,7 +4840,7 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,10 +4855,10 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>11</v>
@@ -4800,13 +4867,13 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>24</v>
@@ -4997,7 +5064,7 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.471</v>
+        <v>0.463</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5056,16 +5123,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O26" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q26" t="n">
         <v>0.781</v>
@@ -5074,7 +5141,7 @@
         <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
         <v>41.6</v>
@@ -5086,7 +5153,7 @@
         <v>14.7</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
@@ -5098,28 +5165,28 @@
         <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB26" t="n">
         <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5140,10 +5207,10 @@
         <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
         <v>7</v>
@@ -5152,7 +5219,7 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
         <v>18</v>
@@ -5164,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>22</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,34 +5296,34 @@
         <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
         <v>7.3</v>
       </c>
       <c r="M27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O27" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
         <v>23</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R27" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T27" t="n">
         <v>40.4</v>
@@ -5274,7 +5341,7 @@
         <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
         <v>21.2</v>
@@ -5286,10 +5353,10 @@
         <v>99.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5298,16 +5365,16 @@
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
         <v>16</v>
@@ -5331,7 +5398,7 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>28</v>
@@ -5349,7 +5416,7 @@
         <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5683,7 +5750,7 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5847,13 +5914,13 @@
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI30" t="n">
         <v>18</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>15</v>
@@ -5877,7 +5944,7 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF31" t="n">
         <v>23</v>
       </c>
-      <c r="AE31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AG31" t="n">
         <v>22</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>23</v>
       </c>
       <c r="AH31" t="n">
         <v>6</v>
@@ -6035,7 +6102,7 @@
         <v>26</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>26</v>
@@ -6065,7 +6132,7 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2012-13</t>
+          <t>2013-03-21</t>
         </is>
       </c>
     </row>
